--- a/evaluation_forms/044_implementation_science_check_in--evaluation_forms.xlsx
+++ b/evaluation_forms/044_implementation_science_check_in--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>quality_improvement_project_1</t>
+          <t>quality improvement project 1</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>quality_improvement_project_2</t>
+          <t>quality improvement project 2</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>quality_improvement_project_3</t>
+          <t>quality improvement project 3</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>quality_improvement_project_4</t>
+          <t>quality improvement project 4</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>quality_improvement_project_5</t>
+          <t>quality improvement project 5</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>implementation_science_1</t>
+          <t>implementation science 1</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>implementation_science_2</t>
+          <t>implementation science 2</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>implementation_science_3</t>
+          <t>implementation science 3</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>implementation_science_4</t>
+          <t>implementation science 4</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>implementation_science_5</t>
+          <t>implementation science 5</t>
         </is>
       </c>
     </row>
